--- a/.vscode/ReportLayouts/Excel/Rep.70021.SupplierVoucherReportExcel.xlsx
+++ b/.vscode/ReportLayouts/Excel/Rep.70021.SupplierVoucherReportExcel.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <x:workbookPr defaultThemeVersion="166925"/>
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <x:workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Radiant\SourceCode\WP-Report\.vscode\ReportLayouts\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rom IT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B86A99-BEF9-4DC9-9139-AF7C94EEDED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1889B9E-B38C-4B4B-94F9-40F642EF3858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <x:workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Data" sheetId="5" r:id="rId1"/>
+    <x:sheet name="Report" sheetId="9" r:id="rId1"/>
+    <x:sheet name="Data" sheetId="5" r:id="rId2"/>
+    <x:sheet name="CaptionData" sheetId="6" r:id="rId3"/>
+    <x:sheet name="Aggregated Metadata" sheetId="7" state="hidden" r:id="rId4"/>
+    <x:sheet name="TranslationData" sheetId="8" state="hidden" r:id="rId5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",#REF!,#REF!,"none",)</x:definedName>
@@ -40,7 +44,10 @@
     <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",#REF!,#REF!,"none",)</x:definedName>
     <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",#REF!,#REF!,"none",)</x:definedName>
   </x:definedNames>
-  <x:calcPr calcId="191029"/>
+  <x:calcPr calcId="191029" forceFullCalc="1"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="8" r:id="rId6"/>
+  </x:pivotCaches>
   <x:extLst>
     <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -57,8 +64,30 @@
 </x:workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
   <si>
     <t>BrandName</t>
   </si>
@@ -79,26 +108,217 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Kiehl s</t>
+  </si>
+  <si>
+    <t>100091</t>
+  </si>
+  <si>
+    <t>L'OREAL VIETNAM CO.,LTD</t>
+  </si>
+  <si>
+    <t>Lancome</t>
+  </si>
+  <si>
+    <t>Mac</t>
+  </si>
+  <si>
+    <t>100090</t>
+  </si>
+  <si>
+    <t>ESTEE LAUDER (VIETNAM) LLC</t>
+  </si>
+  <si>
+    <t>Shu Uemura</t>
+  </si>
+  <si>
+    <t>SKII</t>
+  </si>
+  <si>
+    <t>100664</t>
+  </si>
+  <si>
+    <t>LUXASIA VIETNAM CO.,LTD</t>
+  </si>
+  <si>
+    <t>Caption</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Report Property</t>
+  </si>
+  <si>
+    <t>Report Property Value</t>
+  </si>
+  <si>
+    <t>Request Property</t>
+  </si>
+  <si>
+    <t>Request Property Value</t>
+  </si>
+  <si>
+    <t>Request Page Option</t>
+  </si>
+  <si>
+    <t>Request Page Option Value</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Filter Value</t>
+  </si>
+  <si>
+    <t>Extension ID</t>
+  </si>
+  <si>
+    <t>6dc7cd47-bf68-4031-88d2-04300818fac2</t>
+  </si>
+  <si>
+    <t>Tenant Id</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>DateFilter</t>
+  </si>
+  <si>
+    <t>01/08/25..01/08/25</t>
+  </si>
+  <si>
+    <t>Extension Name</t>
+  </si>
+  <si>
+    <t>worldPOS-Report by World POS Sdn. Bhd</t>
+  </si>
+  <si>
+    <t>Environment name</t>
+  </si>
+  <si>
+    <t>SpecialGroupFilter</t>
+  </si>
+  <si>
+    <t>Extension Publisher</t>
+  </si>
+  <si>
+    <t>World POS Sdn. Bhd</t>
+  </si>
+  <si>
+    <t>Environment type</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>VendorNoFilter</t>
+  </si>
+  <si>
+    <t>Extension Version</t>
+  </si>
+  <si>
+    <t>24.1.0.19</t>
+  </si>
+  <si>
+    <t>Company name</t>
+  </si>
+  <si>
+    <t>HO</t>
+  </si>
+  <si>
+    <t>Object ID</t>
+  </si>
+  <si>
+    <t>Company Id</t>
+  </si>
+  <si>
+    <t>{423CCAD4-A92C-F011-B000-00505693A2C3}</t>
+  </si>
+  <si>
+    <t>Object Name</t>
+  </si>
+  <si>
+    <t>Supplier Voucher Report</t>
+  </si>
+  <si>
+    <t>User name</t>
+  </si>
+  <si>
+    <t>SUPER</t>
+  </si>
+  <si>
+    <t>About This Report Title</t>
+  </si>
+  <si>
+    <t>Supplier Vouche rReport</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>About This Report Text</t>
+  </si>
+  <si>
+    <t>AboutText Supplier Voucher Report</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Report help link</t>
+  </si>
+  <si>
+    <t>Format Region</t>
+  </si>
+  <si>
+    <t>CaptionKey</t>
+  </si>
+  <si>
+    <t>SUPPLIER VOUCHER REPORT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -113,17 +333,142 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="28">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
@@ -154,7 +499,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFC0C0C0"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -172,19 +517,491 @@
 </styleSheet>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Rom IT" refreshedDate="45896.765878472223" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{5CF30BD2-E2AC-4669-924A-C4FAD9421B3D}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Data"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="BrandName" numFmtId="49">
+      <sharedItems count="5">
+        <s v="Kiehl s"/>
+        <s v="Lancome"/>
+        <s v="Mac"/>
+        <s v="Shu Uemura"/>
+        <s v="SKII"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="SupplierCode" numFmtId="49">
+      <sharedItems count="3">
+        <s v="100091"/>
+        <s v="100090"/>
+        <s v="100664"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="SupplierName" numFmtId="49">
+      <sharedItems count="3">
+        <s v="L'OREAL VIETNAM CO.,LTD"/>
+        <s v="ESTEE LAUDER (VIETNAM) LLC"/>
+        <s v="LUXASIA VIETNAM CO.,LTD"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nomination" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="185000" maxValue="1400000" count="6">
+        <n v="185000"/>
+        <n v="200000"/>
+        <n v="1400000"/>
+        <n v="534000"/>
+        <n v="300000"/>
+        <n v="250000"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="15" count="2">
+        <n v="1"/>
+        <n v="15"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TotalAmount" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="185000" maxValue="3750000" count="6">
+        <n v="185000"/>
+        <n v="200000"/>
+        <n v="1400000"/>
+        <n v="534000"/>
+        <n v="300000"/>
+        <n v="3750000"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{657ED345-6BCC-417D-9BC2-164B32EB8BB8}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A4:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="6"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" numFmtId="3" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" numFmtId="3" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" numFmtId="3" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="6">
+    <field x="1"/>
+    <field x="2"/>
+    <field x="0"/>
+    <field x="3"/>
+    <field x="4"/>
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+      <x/>
+      <x v="2"/>
+      <x v="4"/>
+      <x/>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="1"/>
+      <x/>
+      <x/>
+      <x/>
+      <x/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+      <x/>
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+      <x v="5"/>
+      <x/>
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+      <x v="3"/>
+      <x/>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="2"/>
+      <x v="4"/>
+      <x v="2"/>
+      <x v="1"/>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <formats count="24">
+    <format dxfId="23">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="3"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="4"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="5"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="3"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="4"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="5"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="3"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="4"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="5"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="3"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="4"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="5"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Data" displayName="Data" ref="A1:F2" totalsRowShown="0" headerRowDxfId="3" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
-  <x:autoFilter ref="A1:F2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Data" displayName="Data" ref="A1:F7" totalsRowShown="0" headerRowDxfId="27" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:F7" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="BrandName" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
     <x:tableColumn id="2" name="SupplierCode" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
     <x:tableColumn id="3" name="SupplierName" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
-    <x:tableColumn id="4" name="Nomination" dataDxfId="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
-    <x:tableColumn id="5" name="Quantity" dataDxfId="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
-    <x:tableColumn id="6" name="TotalAmount" dataDxfId="0" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="4" name="Nomination" dataDxfId="26" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="5" name="Quantity" dataDxfId="25" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="6" name="TotalAmount" dataDxfId="24" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CaptionData" displayName="CaptionData" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Caption"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ReportMetadataValues" displayName="ReportMetadataValues" ref="A1:B10" totalsRowShown="0">
+  <autoFilter ref="A1:B10" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Report Property"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Report Property Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ReportRequestValues" displayName="ReportRequestValues" ref="D1:E10" totalsRowShown="0">
+  <autoFilter ref="D1:E10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Request Property"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Request Property Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReportRequestPageValues" displayName="ReportRequestPageValues" ref="G1:H4" totalsRowShown="0">
+  <autoFilter ref="G1:H4" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Request Page Option"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Request Page Option Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="ReportFilterValues" displayName="ReportFilterValues" ref="J1:K2" totalsRowShown="0">
+  <autoFilter ref="J1:K2" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Filter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Filter Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="TranslationData" displayName="TranslationData" ref="A1:C2" totalsRowShown="0">
+  <autoFilter ref="A1:C2" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="CaptionKey"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Language"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,8 +1300,208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B0FD83-B0F7-4584-9C96-A05250280524}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2">
+        <v>534000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>534000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>185000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2">
+        <v>200000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2">
+        <v>300000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
+        <v>250000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3750000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -495,44 +1512,188 @@
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2">
+        <v>185000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>200000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2">
+        <v>534000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>534000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>300000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2">
+        <v>250000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3750000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F19:H19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -543,6 +1704,424 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="5" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="5" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>70021</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="3">
+        <v>45896.465424513888</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>1033</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
